--- a/Data/Regression Evidence 2025/Workday_NewHire_Italy_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Italy_Regression_PK17.xlsx
@@ -220,7 +220,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700248</t>
+    <t>10700453</t>
   </si>
   <si>
     <t>Passed</t>
@@ -235,10 +235,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Eliseo</t>
-  </si>
-  <si>
-    <t>Mosciski</t>
+    <t>Sheridan</t>
+  </si>
+  <si>
+    <t>Effertz</t>
   </si>
   <si>
     <t>067898707</t>
@@ -359,7 +359,7 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700249</t>
+    <t>10700454</t>
   </si>
   <si>
     <t>275 Store Management (Gyzag Hopope (10144587))</t>
@@ -368,10 +368,10 @@
     <t>Humberto</t>
   </si>
   <si>
-    <t>Hodkiewicz</t>
-  </si>
-  <si>
-    <t>Auto 78628774</t>
+    <t>Lindgren</t>
+  </si>
+  <si>
+    <t>Auto 52365464</t>
   </si>
   <si>
     <t>Assistant Manager</t>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>71</v>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="Y2" s="16">
         <f t="shared" ref="Y2:Y3" si="2">TODAY()+20</f>
-        <v>45872</v>
+        <v>45893</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>85</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="AT2" s="18">
         <f t="shared" ref="AT2:AT3" si="3">X2-1</f>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AU2" s="18">
         <f t="shared" ref="AU2:AU3" si="4">X2-1</f>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AV2" s="29">
         <f t="shared" ref="AV2:AV3" si="5">AJ2</f>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="BD2" s="33" t="str">
         <f>BH9</f>
-        <v>MTKBNN10D10A354A</v>
+        <v>MTKBNN10D10A316A</v>
       </c>
       <c r="BE2" t="s">
         <v>103</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" si="0"/>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>71</v>
@@ -1499,11 +1499,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="1"/>
-        <v>45821</v>
+        <v>45842</v>
       </c>
       <c r="Y3" s="16">
         <f t="shared" si="2"/>
-        <v>45872</v>
+        <v>45893</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>85</v>
@@ -1567,11 +1567,11 @@
       </c>
       <c r="AT3" s="18">
         <f t="shared" si="3"/>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AU3" s="18">
         <f t="shared" si="4"/>
-        <v>45820</v>
+        <v>45841</v>
       </c>
       <c r="AV3" s="29">
         <f t="shared" si="5"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="BD3" s="33" t="str">
         <f>BH10</f>
-        <v>MTKNBN20D20A151A</v>
+        <v>MTKNBN20D20A222A</v>
       </c>
       <c r="BE3" t="s">
         <v>103</v>
@@ -1670,28 +1670,28 @@
       </c>
       <c r="AX9">
         <f t="array" ref="AX9:AX23">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>22067</v>
+        <v>71627</v>
       </c>
       <c r="AY9" t="s">
         <v>125</v>
       </c>
       <c r="AZ9" t="str">
         <f>AW9&amp;AX9&amp;AY9</f>
-        <v>AB22067JC</v>
+        <v>AB71627JC</v>
       </c>
       <c r="BD9" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE9">
         <f t="array" ref="BE9:BE23">_xlfn.RANDARRAY(15,1,123,999,TRUE)</f>
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="BG9" t="s">
         <v>127</v>
       </c>
       <c r="BH9" t="str">
         <f>BD9&amp;BE9&amp;BF9&amp;BG9</f>
-        <v>MTKBNN10D10A354A</v>
+        <v>MTKBNN10D10A316A</v>
       </c>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1700,27 +1700,27 @@
         <v>128</v>
       </c>
       <c r="AX10">
-        <v>84006</v>
+        <v>24607</v>
       </c>
       <c r="AY10" t="s">
         <v>129</v>
       </c>
       <c r="AZ10" t="str">
         <f t="shared" ref="AZ10:AZ23" si="6">AW10&amp;AX10&amp;AY10</f>
-        <v>BA84006CJ</v>
+        <v>BA24607CJ</v>
       </c>
       <c r="BD10" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE10">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="BG10" t="s">
         <v>127</v>
       </c>
       <c r="BH10" t="str">
         <f t="shared" ref="BH10:BH23" si="7">BD10&amp;BE10&amp;BF10&amp;BG10</f>
-        <v>MTKNBN20D20A151A</v>
+        <v>MTKNBN20D20A222A</v>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1729,27 +1729,27 @@
         <v>124</v>
       </c>
       <c r="AX11">
-        <v>77368</v>
+        <v>63188</v>
       </c>
       <c r="AY11" t="s">
         <v>125</v>
       </c>
       <c r="AZ11" t="str">
         <f t="shared" si="6"/>
-        <v>AB77368JC</v>
+        <v>AB63188JC</v>
       </c>
       <c r="BD11" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE11">
-        <v>891</v>
+        <v>322</v>
       </c>
       <c r="BG11" t="s">
         <v>127</v>
       </c>
       <c r="BH11" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A891A</v>
+        <v>MTKBNN10D10A322A</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1758,27 +1758,27 @@
         <v>128</v>
       </c>
       <c r="AX12">
-        <v>45760</v>
+        <v>81234</v>
       </c>
       <c r="AY12" t="s">
         <v>129</v>
       </c>
       <c r="AZ12" t="str">
         <f t="shared" si="6"/>
-        <v>BA45760CJ</v>
+        <v>BA81234CJ</v>
       </c>
       <c r="BD12" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE12">
-        <v>885</v>
+        <v>630</v>
       </c>
       <c r="BG12" t="s">
         <v>127</v>
       </c>
       <c r="BH12" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A885A</v>
+        <v>MTKNBN20D20A630A</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1787,27 +1787,27 @@
         <v>124</v>
       </c>
       <c r="AX13">
-        <v>27388</v>
+        <v>14440</v>
       </c>
       <c r="AY13" t="s">
         <v>125</v>
       </c>
       <c r="AZ13" t="str">
         <f t="shared" si="6"/>
-        <v>AB27388JC</v>
+        <v>AB14440JC</v>
       </c>
       <c r="BD13" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE13">
-        <v>381</v>
+        <v>210</v>
       </c>
       <c r="BG13" t="s">
         <v>127</v>
       </c>
       <c r="BH13" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A381A</v>
+        <v>MTKBNN10D10A210A</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1816,27 +1816,27 @@
         <v>128</v>
       </c>
       <c r="AX14">
-        <v>31844</v>
+        <v>62973</v>
       </c>
       <c r="AY14" t="s">
         <v>129</v>
       </c>
       <c r="AZ14" t="str">
         <f t="shared" si="6"/>
-        <v>BA31844CJ</v>
+        <v>BA62973CJ</v>
       </c>
       <c r="BD14" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE14">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="BG14" t="s">
         <v>127</v>
       </c>
       <c r="BH14" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A206A</v>
+        <v>MTKNBN20D20A240A</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1845,27 +1845,27 @@
         <v>124</v>
       </c>
       <c r="AX15">
-        <v>49829</v>
+        <v>95116</v>
       </c>
       <c r="AY15" t="s">
         <v>125</v>
       </c>
       <c r="AZ15" t="str">
         <f t="shared" si="6"/>
-        <v>AB49829JC</v>
+        <v>AB95116JC</v>
       </c>
       <c r="BD15" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE15">
-        <v>180</v>
+        <v>777</v>
       </c>
       <c r="BG15" t="s">
         <v>127</v>
       </c>
       <c r="BH15" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A180A</v>
+        <v>MTKBNN10D10A777A</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1874,27 +1874,27 @@
         <v>128</v>
       </c>
       <c r="AX16">
-        <v>45309</v>
+        <v>12952</v>
       </c>
       <c r="AY16" t="s">
         <v>129</v>
       </c>
       <c r="AZ16" t="str">
         <f t="shared" si="6"/>
-        <v>BA45309CJ</v>
+        <v>BA12952CJ</v>
       </c>
       <c r="BD16" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE16">
-        <v>834</v>
+        <v>430</v>
       </c>
       <c r="BG16" t="s">
         <v>127</v>
       </c>
       <c r="BH16" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A834A</v>
+        <v>MTKNBN20D20A430A</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1903,27 +1903,27 @@
         <v>124</v>
       </c>
       <c r="AX17">
-        <v>33664</v>
+        <v>70143</v>
       </c>
       <c r="AY17" t="s">
         <v>125</v>
       </c>
       <c r="AZ17" t="str">
         <f t="shared" si="6"/>
-        <v>AB33664JC</v>
+        <v>AB70143JC</v>
       </c>
       <c r="BD17" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE17">
-        <v>261</v>
+        <v>782</v>
       </c>
       <c r="BG17" t="s">
         <v>127</v>
       </c>
       <c r="BH17" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A261A</v>
+        <v>MTKBNN10D10A782A</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:60" x14ac:dyDescent="0.25">
@@ -1932,27 +1932,27 @@
         <v>128</v>
       </c>
       <c r="AX18">
-        <v>96141</v>
+        <v>94645</v>
       </c>
       <c r="AY18" t="s">
         <v>129</v>
       </c>
       <c r="AZ18" t="str">
         <f t="shared" si="6"/>
-        <v>BA96141CJ</v>
+        <v>BA94645CJ</v>
       </c>
       <c r="BD18" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE18">
-        <v>880</v>
+        <v>196</v>
       </c>
       <c r="BG18" t="s">
         <v>127</v>
       </c>
       <c r="BH18" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A880A</v>
+        <v>MTKNBN20D20A196A</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1960,27 +1960,27 @@
         <v>124</v>
       </c>
       <c r="AX19">
-        <v>38903</v>
+        <v>94260</v>
       </c>
       <c r="AY19" t="s">
         <v>125</v>
       </c>
       <c r="AZ19" t="str">
         <f t="shared" si="6"/>
-        <v>AB38903JC</v>
+        <v>AB94260JC</v>
       </c>
       <c r="BD19" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE19">
-        <v>869</v>
+        <v>759</v>
       </c>
       <c r="BG19" t="s">
         <v>127</v>
       </c>
       <c r="BH19" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A869A</v>
+        <v>MTKBNN10D10A759A</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -1988,27 +1988,27 @@
         <v>128</v>
       </c>
       <c r="AX20">
-        <v>42436</v>
+        <v>41818</v>
       </c>
       <c r="AY20" t="s">
         <v>129</v>
       </c>
       <c r="AZ20" t="str">
         <f t="shared" si="6"/>
-        <v>BA42436CJ</v>
+        <v>BA41818CJ</v>
       </c>
       <c r="BD20" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE20">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A355A</v>
+        <v>MTKNBN20D20A130A</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2016,27 +2016,27 @@
         <v>124</v>
       </c>
       <c r="AX21">
-        <v>57739</v>
+        <v>30487</v>
       </c>
       <c r="AY21" t="s">
         <v>125</v>
       </c>
       <c r="AZ21" t="str">
         <f t="shared" si="6"/>
-        <v>AB57739JC</v>
+        <v>AB30487JC</v>
       </c>
       <c r="BD21" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE21">
-        <v>419</v>
+        <v>284</v>
       </c>
       <c r="BG21" t="s">
         <v>127</v>
       </c>
       <c r="BH21" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A419A</v>
+        <v>MTKBNN10D10A284A</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2044,27 +2044,27 @@
         <v>128</v>
       </c>
       <c r="AX22">
-        <v>31447</v>
+        <v>88497</v>
       </c>
       <c r="AY22" t="s">
         <v>129</v>
       </c>
       <c r="AZ22" t="str">
         <f t="shared" si="6"/>
-        <v>BA31447CJ</v>
+        <v>BA88497CJ</v>
       </c>
       <c r="BD22" s="33" t="s">
         <v>130</v>
       </c>
       <c r="BE22">
-        <v>632</v>
+        <v>462</v>
       </c>
       <c r="BG22" t="s">
         <v>127</v>
       </c>
       <c r="BH22" t="str">
         <f t="shared" si="7"/>
-        <v>MTKNBN20D20A632A</v>
+        <v>MTKNBN20D20A462A</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="49:60" x14ac:dyDescent="0.25">
@@ -2072,27 +2072,27 @@
         <v>124</v>
       </c>
       <c r="AX23">
-        <v>18459</v>
+        <v>81370</v>
       </c>
       <c r="AY23" t="s">
         <v>125</v>
       </c>
       <c r="AZ23" t="str">
         <f t="shared" si="6"/>
-        <v>AB18459JC</v>
+        <v>AB81370JC</v>
       </c>
       <c r="BD23" s="33" t="s">
         <v>126</v>
       </c>
       <c r="BE23">
-        <v>598</v>
+        <v>135</v>
       </c>
       <c r="BG23" t="s">
         <v>127</v>
       </c>
       <c r="BH23" t="str">
         <f t="shared" si="7"/>
-        <v>MTKBNN10D10A598A</v>
+        <v>MTKBNN10D10A135A</v>
       </c>
     </row>
   </sheetData>
